--- a/backtest_runs/20260410_193731/by_symbol/ESBL/ESBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ESBL/ESBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-13812.74999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>86187.25000000001</v>
@@ -679,7 +679,7 @@
         <v>-13497.03000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>86818.69000000002</v>
@@ -725,7 +725,7 @@
         <v>-12234.15000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>74584.54000000001</v>
@@ -771,7 +771,7 @@
         <v>-8919.090000000006</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>65665.45000000001</v>
@@ -909,7 +909,7 @@
         <v>-947.1600000000078</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>72690.22000000002</v>
@@ -955,7 +955,7 @@
         <v>-2762.549999999997</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>69927.67000000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5919.75</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>64007.92000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-1894.320000000002</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>62113.60000000001</v>
@@ -1139,7 +1139,7 @@
         <v>-947.1599999999938</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>63218.62000000002</v>
@@ -1185,7 +1185,7 @@
         <v>-4025.429999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>59193.19000000002</v>
@@ -1231,7 +1231,7 @@
         <v>-552.5100000000023</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>58640.68000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-9629.460000000005</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>49011.22000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-8682.299999999997</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>40328.92000000001</v>
@@ -1369,7 +1369,7 @@
         <v>-315.7200000000073</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>40013.2</v>
@@ -1461,7 +1461,7 @@
         <v>-7024.76999999999</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>40092.13000000002</v>
